--- a/artfynd/A 46264-2023 artfynd.xlsx
+++ b/artfynd/A 46264-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 46264-2023 artfynd.xlsx
+++ b/artfynd/A 46264-2023 artfynd.xlsx
@@ -2727,7 +2727,7 @@
         <v>116177734</v>
       </c>
       <c r="B19" t="n">
-        <v>57265</v>
+        <v>57478</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Långtjärnen (Långtjärnen), Mpd</t>
+          <t>Långtjärnen, Långtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">

--- a/artfynd/A 46264-2023 artfynd.xlsx
+++ b/artfynd/A 46264-2023 artfynd.xlsx
@@ -2731,7 +2731,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">

--- a/artfynd/A 46264-2023 artfynd.xlsx
+++ b/artfynd/A 46264-2023 artfynd.xlsx
@@ -2727,7 +2727,7 @@
         <v>116177734</v>
       </c>
       <c r="B19" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 46264-2023 artfynd.xlsx
+++ b/artfynd/A 46264-2023 artfynd.xlsx
@@ -2727,7 +2727,7 @@
         <v>116177734</v>
       </c>
       <c r="B19" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
